--- a/artfynd/A 3933-2025 artfynd.xlsx
+++ b/artfynd/A 3933-2025 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86442966</v>
+        <v>85622082</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hundnorberget, Vb</t>
+          <t>Sörträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755030.9907378478</v>
+        <v>755305</v>
       </c>
       <c r="R2" t="n">
-        <v>7141686.205801155</v>
+        <v>7141917</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,35 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>86442968</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755191.0764156848</v>
+        <v>755191</v>
       </c>
       <c r="R3" t="n">
-        <v>7141529.971803529</v>
+        <v>7141530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +840,9 @@
           <t>2020-06-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +876,7 @@
         <v>86442967</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755189.9202585442</v>
+        <v>755190</v>
       </c>
       <c r="R4" t="n">
-        <v>7141528.131931782</v>
+        <v>7141528</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +941,9 @@
           <t>2020-06-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3933-2025 artfynd.xlsx
+++ b/artfynd/A 3933-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85622082</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86442968</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,8 +986,18 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86442967</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>